--- a/output/graficos_nacionales/plot_nacional_e_supneta_a_2024.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_supneta_a_2024.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1382,7 +1382,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -4878,7 +4878,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -5108,7 +5108,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -5384,7 +5384,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -5752,7 +5752,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -5982,7 +5982,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -6580,7 +6580,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -6626,7 +6626,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -6672,7 +6672,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -6764,7 +6764,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -7040,7 +7040,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -7132,7 +7132,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -7178,7 +7178,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -7270,7 +7270,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -7638,7 +7638,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -8190,7 +8190,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -8282,7 +8282,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -8374,7 +8374,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -8512,7 +8512,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -9064,7 +9064,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -9754,7 +9754,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -10122,7 +10122,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -10306,7 +10306,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -10398,7 +10398,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -10490,7 +10490,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -10582,7 +10582,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -10628,7 +10628,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -10720,7 +10720,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -10766,7 +10766,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -10812,7 +10812,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -10858,7 +10858,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -10950,7 +10950,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -10996,7 +10996,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -11042,7 +11042,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -11134,7 +11134,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -11180,7 +11180,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -11226,7 +11226,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -11272,7 +11272,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -11318,7 +11318,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -11410,7 +11410,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -11502,7 +11502,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -11640,7 +11640,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -11686,7 +11686,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -11732,7 +11732,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -11870,7 +11870,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -11916,7 +11916,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -11962,7 +11962,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -12100,7 +12100,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -12146,7 +12146,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -12284,7 +12284,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -12330,7 +12330,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -12514,7 +12514,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -12560,7 +12560,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -12606,7 +12606,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -12652,7 +12652,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -12790,7 +12790,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -12882,7 +12882,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -12928,7 +12928,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -13020,7 +13020,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -13066,7 +13066,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -13112,7 +13112,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -13204,7 +13204,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -13250,7 +13250,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -13342,7 +13342,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -13388,7 +13388,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -13434,7 +13434,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -13480,7 +13480,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -13526,7 +13526,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -13756,7 +13756,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -13802,7 +13802,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -13848,7 +13848,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -13894,7 +13894,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -13986,7 +13986,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -14032,7 +14032,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -14078,7 +14078,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -14170,7 +14170,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -14262,7 +14262,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -14446,7 +14446,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -14584,7 +14584,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -14676,7 +14676,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -14814,7 +14814,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -14998,7 +14998,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -15044,7 +15044,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -15182,7 +15182,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -15320,7 +15320,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">

--- a/output/graficos_nacionales/plot_nacional_e_supneta_a_2024.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_supneta_a_2024.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="700" uniqueCount="700">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="697">
   <si>
     <t xml:space="preserve">year</t>
   </si>
@@ -1189,15 +1189,6 @@
     <t xml:space="preserve">Diego de Almagro</t>
   </si>
   <si>
-    <t xml:space="preserve">Arica y Parinacota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arica</t>
-  </si>
-  <si>
     <t xml:space="preserve">3101</t>
   </si>
   <si>
@@ -2071,7 +2062,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-30 15:51</t>
+    <t xml:space="preserve">2026-09-07 12:55</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -2483,7 +2474,7 @@
   <cols>
     <col min="1" max="1" width="10.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="11.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="20.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="15.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="12.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="22.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="14.71" hidden="0" customWidth="1"/>
@@ -8354,16 +8345,16 @@
         <v>2024</v>
       </c>
       <c r="B184" s="2" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C184" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="D184" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="D184" s="2" t="s">
+      <c r="E184" s="2" t="s">
         <v>391</v>
-      </c>
-      <c r="E184" s="2" t="s">
-        <v>392</v>
       </c>
       <c r="F184" s="2" t="s">
         <v>385</v>
@@ -8375,7 +8366,7 @@
         <v>15</v>
       </c>
       <c r="I184" s="2" t="n">
-        <v>50.73</v>
+        <v>49.31</v>
       </c>
       <c r="J184" s="2" t="s">
         <v>16</v>
@@ -8386,16 +8377,16 @@
         <v>2024</v>
       </c>
       <c r="B185" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E185" s="2" t="s">
-        <v>394</v>
+        <v>382</v>
       </c>
       <c r="F185" s="2" t="s">
         <v>385</v>
@@ -8407,7 +8398,7 @@
         <v>15</v>
       </c>
       <c r="I185" s="2" t="n">
-        <v>49.31</v>
+        <v>48.88</v>
       </c>
       <c r="J185" s="2" t="s">
         <v>16</v>
@@ -8418,16 +8409,16 @@
         <v>2024</v>
       </c>
       <c r="B186" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>382</v>
+        <v>393</v>
       </c>
       <c r="D186" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="E186" s="2" t="s">
         <v>395</v>
-      </c>
-      <c r="E186" s="2" t="s">
-        <v>382</v>
       </c>
       <c r="F186" s="2" t="s">
         <v>385</v>
@@ -8439,7 +8430,7 @@
         <v>15</v>
       </c>
       <c r="I186" s="2" t="n">
-        <v>48.88</v>
+        <v>48.37</v>
       </c>
       <c r="J186" s="2" t="s">
         <v>16</v>
@@ -8450,16 +8441,16 @@
         <v>2024</v>
       </c>
       <c r="B187" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C187" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="D187" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="D187" s="2" t="s">
+      <c r="E187" s="2" t="s">
         <v>397</v>
-      </c>
-      <c r="E187" s="2" t="s">
-        <v>398</v>
       </c>
       <c r="F187" s="2" t="s">
         <v>385</v>
@@ -8471,7 +8462,7 @@
         <v>15</v>
       </c>
       <c r="I187" s="2" t="n">
-        <v>48.37</v>
+        <v>48.35</v>
       </c>
       <c r="J187" s="2" t="s">
         <v>16</v>
@@ -8482,16 +8473,16 @@
         <v>2024</v>
       </c>
       <c r="B188" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>382</v>
+        <v>393</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="F188" s="2" t="s">
         <v>385</v>
@@ -8503,7 +8494,7 @@
         <v>15</v>
       </c>
       <c r="I188" s="2" t="n">
-        <v>48.35</v>
+        <v>48.1</v>
       </c>
       <c r="J188" s="2" t="s">
         <v>16</v>
@@ -8514,16 +8505,16 @@
         <v>2024</v>
       </c>
       <c r="B189" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="D189" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="E189" s="2" t="s">
         <v>401</v>
-      </c>
-      <c r="E189" s="2" t="s">
-        <v>396</v>
       </c>
       <c r="F189" s="2" t="s">
         <v>385</v>
@@ -8535,7 +8526,7 @@
         <v>15</v>
       </c>
       <c r="I189" s="2" t="n">
-        <v>48.1</v>
+        <v>47.37</v>
       </c>
       <c r="J189" s="2" t="s">
         <v>16</v>
@@ -8549,13 +8540,13 @@
         <v>1</v>
       </c>
       <c r="C190" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="D190" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="D190" s="2" t="s">
+      <c r="E190" s="2" t="s">
         <v>403</v>
-      </c>
-      <c r="E190" s="2" t="s">
-        <v>404</v>
       </c>
       <c r="F190" s="2" t="s">
         <v>385</v>
@@ -8567,7 +8558,7 @@
         <v>15</v>
       </c>
       <c r="I190" s="2" t="n">
-        <v>47.37</v>
+        <v>47.22</v>
       </c>
       <c r="J190" s="2" t="s">
         <v>16</v>
@@ -8578,16 +8569,16 @@
         <v>2024</v>
       </c>
       <c r="B191" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>402</v>
+        <v>382</v>
       </c>
       <c r="D191" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="E191" s="2" t="s">
         <v>405</v>
-      </c>
-      <c r="E191" s="2" t="s">
-        <v>406</v>
       </c>
       <c r="F191" s="2" t="s">
         <v>385</v>
@@ -8599,7 +8590,7 @@
         <v>15</v>
       </c>
       <c r="I191" s="2" t="n">
-        <v>47.22</v>
+        <v>47.09</v>
       </c>
       <c r="J191" s="2" t="s">
         <v>16</v>
@@ -8610,16 +8601,16 @@
         <v>2024</v>
       </c>
       <c r="B192" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>382</v>
+        <v>393</v>
       </c>
       <c r="D192" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="E192" s="2" t="s">
         <v>407</v>
-      </c>
-      <c r="E192" s="2" t="s">
-        <v>408</v>
       </c>
       <c r="F192" s="2" t="s">
         <v>385</v>
@@ -8631,7 +8622,7 @@
         <v>15</v>
       </c>
       <c r="I192" s="2" t="n">
-        <v>47.09</v>
+        <v>46.53</v>
       </c>
       <c r="J192" s="2" t="s">
         <v>16</v>
@@ -8642,16 +8633,16 @@
         <v>2024</v>
       </c>
       <c r="B193" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>396</v>
+        <v>382</v>
       </c>
       <c r="D193" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="E193" s="2" t="s">
         <v>409</v>
-      </c>
-      <c r="E193" s="2" t="s">
-        <v>410</v>
       </c>
       <c r="F193" s="2" t="s">
         <v>385</v>
@@ -8663,7 +8654,7 @@
         <v>15</v>
       </c>
       <c r="I193" s="2" t="n">
-        <v>46.53</v>
+        <v>45.61</v>
       </c>
       <c r="J193" s="2" t="s">
         <v>16</v>
@@ -8674,16 +8665,16 @@
         <v>2024</v>
       </c>
       <c r="B194" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>382</v>
+        <v>393</v>
       </c>
       <c r="D194" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="E194" s="2" t="s">
         <v>411</v>
-      </c>
-      <c r="E194" s="2" t="s">
-        <v>412</v>
       </c>
       <c r="F194" s="2" t="s">
         <v>385</v>
@@ -8695,7 +8686,7 @@
         <v>15</v>
       </c>
       <c r="I194" s="2" t="n">
-        <v>45.61</v>
+        <v>45.59</v>
       </c>
       <c r="J194" s="2" t="s">
         <v>16</v>
@@ -8706,16 +8697,16 @@
         <v>2024</v>
       </c>
       <c r="B195" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>396</v>
+        <v>382</v>
       </c>
       <c r="D195" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="E195" s="2" t="s">
         <v>413</v>
-      </c>
-      <c r="E195" s="2" t="s">
-        <v>414</v>
       </c>
       <c r="F195" s="2" t="s">
         <v>385</v>
@@ -8727,7 +8718,7 @@
         <v>15</v>
       </c>
       <c r="I195" s="2" t="n">
-        <v>45.59</v>
+        <v>45.51</v>
       </c>
       <c r="J195" s="2" t="s">
         <v>16</v>
@@ -8744,10 +8735,10 @@
         <v>382</v>
       </c>
       <c r="D196" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="E196" s="2" t="s">
         <v>415</v>
-      </c>
-      <c r="E196" s="2" t="s">
-        <v>416</v>
       </c>
       <c r="F196" s="2" t="s">
         <v>385</v>
@@ -8759,7 +8750,7 @@
         <v>15</v>
       </c>
       <c r="I196" s="2" t="n">
-        <v>45.51</v>
+        <v>45.39</v>
       </c>
       <c r="J196" s="2" t="s">
         <v>16</v>
@@ -8776,10 +8767,10 @@
         <v>382</v>
       </c>
       <c r="D197" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="E197" s="2" t="s">
         <v>417</v>
-      </c>
-      <c r="E197" s="2" t="s">
-        <v>418</v>
       </c>
       <c r="F197" s="2" t="s">
         <v>385</v>
@@ -8791,7 +8782,7 @@
         <v>15</v>
       </c>
       <c r="I197" s="2" t="n">
-        <v>45.39</v>
+        <v>44.5</v>
       </c>
       <c r="J197" s="2" t="s">
         <v>16</v>
@@ -8808,10 +8799,10 @@
         <v>382</v>
       </c>
       <c r="D198" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="E198" s="2" t="s">
         <v>419</v>
-      </c>
-      <c r="E198" s="2" t="s">
-        <v>420</v>
       </c>
       <c r="F198" s="2" t="s">
         <v>385</v>
@@ -8823,7 +8814,7 @@
         <v>15</v>
       </c>
       <c r="I198" s="2" t="n">
-        <v>44.5</v>
+        <v>43.89</v>
       </c>
       <c r="J198" s="2" t="s">
         <v>16</v>
@@ -8834,16 +8825,16 @@
         <v>2024</v>
       </c>
       <c r="B199" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="D199" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="E199" s="2" t="s">
         <v>421</v>
-      </c>
-      <c r="E199" s="2" t="s">
-        <v>422</v>
       </c>
       <c r="F199" s="2" t="s">
         <v>385</v>
@@ -8855,7 +8846,7 @@
         <v>15</v>
       </c>
       <c r="I199" s="2" t="n">
-        <v>43.89</v>
+        <v>43.86</v>
       </c>
       <c r="J199" s="2" t="s">
         <v>16</v>
@@ -8872,10 +8863,10 @@
         <v>387</v>
       </c>
       <c r="D200" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="E200" s="2" t="s">
         <v>423</v>
-      </c>
-      <c r="E200" s="2" t="s">
-        <v>424</v>
       </c>
       <c r="F200" s="2" t="s">
         <v>385</v>
@@ -8887,7 +8878,7 @@
         <v>15</v>
       </c>
       <c r="I200" s="2" t="n">
-        <v>43.86</v>
+        <v>43.65</v>
       </c>
       <c r="J200" s="2" t="s">
         <v>16</v>
@@ -8898,16 +8889,16 @@
         <v>2024</v>
       </c>
       <c r="B201" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="D201" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="E201" s="2" t="s">
         <v>425</v>
-      </c>
-      <c r="E201" s="2" t="s">
-        <v>426</v>
       </c>
       <c r="F201" s="2" t="s">
         <v>385</v>
@@ -8919,7 +8910,7 @@
         <v>15</v>
       </c>
       <c r="I201" s="2" t="n">
-        <v>43.65</v>
+        <v>42.58</v>
       </c>
       <c r="J201" s="2" t="s">
         <v>16</v>
@@ -8930,16 +8921,16 @@
         <v>2024</v>
       </c>
       <c r="B202" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="D202" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="E202" s="2" t="s">
         <v>427</v>
-      </c>
-      <c r="E202" s="2" t="s">
-        <v>428</v>
       </c>
       <c r="F202" s="2" t="s">
         <v>385</v>
@@ -8951,7 +8942,7 @@
         <v>15</v>
       </c>
       <c r="I202" s="2" t="n">
-        <v>42.58</v>
+        <v>42.43</v>
       </c>
       <c r="J202" s="2" t="s">
         <v>16</v>
@@ -8962,16 +8953,16 @@
         <v>2024</v>
       </c>
       <c r="B203" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="D203" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="E203" s="2" t="s">
         <v>429</v>
-      </c>
-      <c r="E203" s="2" t="s">
-        <v>430</v>
       </c>
       <c r="F203" s="2" t="s">
         <v>385</v>
@@ -8983,7 +8974,7 @@
         <v>15</v>
       </c>
       <c r="I203" s="2" t="n">
-        <v>42.43</v>
+        <v>41.82</v>
       </c>
       <c r="J203" s="2" t="s">
         <v>16</v>
@@ -8994,16 +8985,16 @@
         <v>2024</v>
       </c>
       <c r="B204" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>382</v>
+        <v>399</v>
       </c>
       <c r="D204" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="E204" s="2" t="s">
         <v>431</v>
-      </c>
-      <c r="E204" s="2" t="s">
-        <v>432</v>
       </c>
       <c r="F204" s="2" t="s">
         <v>385</v>
@@ -9015,7 +9006,7 @@
         <v>15</v>
       </c>
       <c r="I204" s="2" t="n">
-        <v>41.82</v>
+        <v>41.6</v>
       </c>
       <c r="J204" s="2" t="s">
         <v>16</v>
@@ -9026,16 +9017,16 @@
         <v>2024</v>
       </c>
       <c r="B205" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>402</v>
+        <v>382</v>
       </c>
       <c r="D205" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="E205" s="2" t="s">
         <v>433</v>
-      </c>
-      <c r="E205" s="2" t="s">
-        <v>434</v>
       </c>
       <c r="F205" s="2" t="s">
         <v>385</v>
@@ -9047,7 +9038,7 @@
         <v>15</v>
       </c>
       <c r="I205" s="2" t="n">
-        <v>41.6</v>
+        <v>41.51</v>
       </c>
       <c r="J205" s="2" t="s">
         <v>16</v>
@@ -9064,10 +9055,10 @@
         <v>382</v>
       </c>
       <c r="D206" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="E206" s="2" t="s">
         <v>435</v>
-      </c>
-      <c r="E206" s="2" t="s">
-        <v>436</v>
       </c>
       <c r="F206" s="2" t="s">
         <v>385</v>
@@ -9079,7 +9070,7 @@
         <v>15</v>
       </c>
       <c r="I206" s="2" t="n">
-        <v>41.51</v>
+        <v>41.44</v>
       </c>
       <c r="J206" s="2" t="s">
         <v>16</v>
@@ -9090,16 +9081,16 @@
         <v>2024</v>
       </c>
       <c r="B207" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="D207" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="E207" s="2" t="s">
         <v>437</v>
-      </c>
-      <c r="E207" s="2" t="s">
-        <v>438</v>
       </c>
       <c r="F207" s="2" t="s">
         <v>385</v>
@@ -9111,7 +9102,7 @@
         <v>15</v>
       </c>
       <c r="I207" s="2" t="n">
-        <v>41.44</v>
+        <v>41.27</v>
       </c>
       <c r="J207" s="2" t="s">
         <v>16</v>
@@ -9122,16 +9113,16 @@
         <v>2024</v>
       </c>
       <c r="B208" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="D208" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="E208" s="2" t="s">
         <v>439</v>
-      </c>
-      <c r="E208" s="2" t="s">
-        <v>440</v>
       </c>
       <c r="F208" s="2" t="s">
         <v>385</v>
@@ -9143,7 +9134,7 @@
         <v>15</v>
       </c>
       <c r="I208" s="2" t="n">
-        <v>41.27</v>
+        <v>39.29</v>
       </c>
       <c r="J208" s="2" t="s">
         <v>16</v>
@@ -9154,16 +9145,16 @@
         <v>2024</v>
       </c>
       <c r="B209" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="D209" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="E209" s="2" t="s">
         <v>441</v>
-      </c>
-      <c r="E209" s="2" t="s">
-        <v>442</v>
       </c>
       <c r="F209" s="2" t="s">
         <v>385</v>
@@ -9175,7 +9166,7 @@
         <v>15</v>
       </c>
       <c r="I209" s="2" t="n">
-        <v>39.29</v>
+        <v>39.27</v>
       </c>
       <c r="J209" s="2" t="s">
         <v>16</v>
@@ -9186,16 +9177,16 @@
         <v>2024</v>
       </c>
       <c r="B210" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="D210" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="E210" s="2" t="s">
         <v>443</v>
-      </c>
-      <c r="E210" s="2" t="s">
-        <v>444</v>
       </c>
       <c r="F210" s="2" t="s">
         <v>385</v>
@@ -9207,7 +9198,7 @@
         <v>15</v>
       </c>
       <c r="I210" s="2" t="n">
-        <v>39.27</v>
+        <v>39.08</v>
       </c>
       <c r="J210" s="2" t="s">
         <v>16</v>
@@ -9221,13 +9212,13 @@
         <v>2</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="D211" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="E211" s="2" t="s">
         <v>445</v>
-      </c>
-      <c r="E211" s="2" t="s">
-        <v>446</v>
       </c>
       <c r="F211" s="2" t="s">
         <v>385</v>
@@ -9239,7 +9230,7 @@
         <v>15</v>
       </c>
       <c r="I211" s="2" t="n">
-        <v>39.08</v>
+        <v>38.97</v>
       </c>
       <c r="J211" s="2" t="s">
         <v>16</v>
@@ -9250,16 +9241,16 @@
         <v>2024</v>
       </c>
       <c r="B212" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="D212" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="E212" s="2" t="s">
         <v>447</v>
-      </c>
-      <c r="E212" s="2" t="s">
-        <v>448</v>
       </c>
       <c r="F212" s="2" t="s">
         <v>385</v>
@@ -9271,7 +9262,7 @@
         <v>15</v>
       </c>
       <c r="I212" s="2" t="n">
-        <v>38.97</v>
+        <v>38.47</v>
       </c>
       <c r="J212" s="2" t="s">
         <v>16</v>
@@ -9282,16 +9273,16 @@
         <v>2024</v>
       </c>
       <c r="B213" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>402</v>
+        <v>387</v>
       </c>
       <c r="D213" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="E213" s="2" t="s">
         <v>449</v>
-      </c>
-      <c r="E213" s="2" t="s">
-        <v>450</v>
       </c>
       <c r="F213" s="2" t="s">
         <v>385</v>
@@ -9303,7 +9294,7 @@
         <v>15</v>
       </c>
       <c r="I213" s="2" t="n">
-        <v>38.47</v>
+        <v>37.83</v>
       </c>
       <c r="J213" s="2" t="s">
         <v>16</v>
@@ -9314,16 +9305,16 @@
         <v>2024</v>
       </c>
       <c r="B214" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="D214" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="E214" s="2" t="s">
         <v>451</v>
-      </c>
-      <c r="E214" s="2" t="s">
-        <v>452</v>
       </c>
       <c r="F214" s="2" t="s">
         <v>385</v>
@@ -9335,7 +9326,7 @@
         <v>15</v>
       </c>
       <c r="I214" s="2" t="n">
-        <v>37.83</v>
+        <v>34.5</v>
       </c>
       <c r="J214" s="2" t="s">
         <v>16</v>
@@ -9346,16 +9337,16 @@
         <v>2024</v>
       </c>
       <c r="B215" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="D215" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="E215" s="2" t="s">
         <v>453</v>
-      </c>
-      <c r="E215" s="2" t="s">
-        <v>454</v>
       </c>
       <c r="F215" s="2" t="s">
         <v>385</v>
@@ -9367,7 +9358,7 @@
         <v>15</v>
       </c>
       <c r="I215" s="2" t="n">
-        <v>34.5</v>
+        <v>34.23</v>
       </c>
       <c r="J215" s="2" t="s">
         <v>16</v>
@@ -9378,16 +9369,16 @@
         <v>2024</v>
       </c>
       <c r="B216" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="D216" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="E216" s="2" t="s">
         <v>455</v>
-      </c>
-      <c r="E216" s="2" t="s">
-        <v>456</v>
       </c>
       <c r="F216" s="2" t="s">
         <v>385</v>
@@ -9399,7 +9390,7 @@
         <v>15</v>
       </c>
       <c r="I216" s="2" t="n">
-        <v>34.23</v>
+        <v>33.02</v>
       </c>
       <c r="J216" s="2" t="s">
         <v>16</v>
@@ -9410,16 +9401,16 @@
         <v>2024</v>
       </c>
       <c r="B217" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>402</v>
+        <v>382</v>
       </c>
       <c r="D217" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="E217" s="2" t="s">
         <v>457</v>
-      </c>
-      <c r="E217" s="2" t="s">
-        <v>458</v>
       </c>
       <c r="F217" s="2" t="s">
         <v>385</v>
@@ -9431,7 +9422,7 @@
         <v>15</v>
       </c>
       <c r="I217" s="2" t="n">
-        <v>33.02</v>
+        <v>32.48</v>
       </c>
       <c r="J217" s="2" t="s">
         <v>16</v>
@@ -9442,16 +9433,16 @@
         <v>2024</v>
       </c>
       <c r="B218" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>382</v>
+        <v>399</v>
       </c>
       <c r="D218" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="E218" s="2" t="s">
         <v>459</v>
-      </c>
-      <c r="E218" s="2" t="s">
-        <v>460</v>
       </c>
       <c r="F218" s="2" t="s">
         <v>385</v>
@@ -9463,7 +9454,7 @@
         <v>15</v>
       </c>
       <c r="I218" s="2" t="n">
-        <v>32.48</v>
+        <v>31.31</v>
       </c>
       <c r="J218" s="2" t="s">
         <v>16</v>
@@ -9477,13 +9468,13 @@
         <v>1</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="D219" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="E219" s="2" t="s">
         <v>461</v>
-      </c>
-      <c r="E219" s="2" t="s">
-        <v>462</v>
       </c>
       <c r="F219" s="2" t="s">
         <v>385</v>
@@ -9495,7 +9486,7 @@
         <v>15</v>
       </c>
       <c r="I219" s="2" t="n">
-        <v>31.31</v>
+        <v>30.37</v>
       </c>
       <c r="J219" s="2" t="s">
         <v>16</v>
@@ -9506,10 +9497,10 @@
         <v>2024</v>
       </c>
       <c r="B220" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>402</v>
+        <v>462</v>
       </c>
       <c r="D220" s="2" t="s">
         <v>463</v>
@@ -9518,16 +9509,16 @@
         <v>464</v>
       </c>
       <c r="F220" s="2" t="s">
-        <v>385</v>
+        <v>465</v>
       </c>
       <c r="G220" s="2" t="s">
-        <v>386</v>
+        <v>466</v>
       </c>
       <c r="H220" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I220" s="2" t="n">
-        <v>30.37</v>
+        <v>58.74</v>
       </c>
       <c r="J220" s="2" t="s">
         <v>16</v>
@@ -9541,25 +9532,25 @@
         <v>8</v>
       </c>
       <c r="C221" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="D221" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="E221" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="F221" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="D221" s="2" t="s">
+      <c r="G221" s="2" t="s">
         <v>466</v>
       </c>
-      <c r="E221" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="F221" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="G221" s="2" t="s">
-        <v>469</v>
-      </c>
       <c r="H221" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I221" s="2" t="n">
-        <v>58.74</v>
+        <v>58.44</v>
       </c>
       <c r="J221" s="2" t="s">
         <v>16</v>
@@ -9573,25 +9564,25 @@
         <v>8</v>
       </c>
       <c r="C222" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="D222" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="E222" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="F222" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="D222" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="E222" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="F222" s="2" t="s">
-        <v>468</v>
-      </c>
       <c r="G222" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H222" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I222" s="2" t="n">
-        <v>58.44</v>
+        <v>56.61</v>
       </c>
       <c r="J222" s="2" t="s">
         <v>16</v>
@@ -9605,25 +9596,25 @@
         <v>8</v>
       </c>
       <c r="C223" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="D223" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="E223" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="F223" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="D223" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="E223" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="F223" s="2" t="s">
-        <v>468</v>
-      </c>
       <c r="G223" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H223" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I223" s="2" t="n">
-        <v>56.61</v>
+        <v>56.28</v>
       </c>
       <c r="J223" s="2" t="s">
         <v>16</v>
@@ -9634,10 +9625,10 @@
         <v>2024</v>
       </c>
       <c r="B224" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="D224" s="2" t="s">
         <v>474</v>
@@ -9646,16 +9637,16 @@
         <v>475</v>
       </c>
       <c r="F224" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G224" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H224" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I224" s="2" t="n">
-        <v>56.28</v>
+        <v>55.28</v>
       </c>
       <c r="J224" s="2" t="s">
         <v>16</v>
@@ -9666,28 +9657,28 @@
         <v>2024</v>
       </c>
       <c r="B225" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C225" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="D225" s="2" t="s">
         <v>476</v>
       </c>
-      <c r="D225" s="2" t="s">
+      <c r="E225" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="E225" s="2" t="s">
-        <v>478</v>
-      </c>
       <c r="F225" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G225" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H225" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I225" s="2" t="n">
-        <v>55.28</v>
+        <v>54.94</v>
       </c>
       <c r="J225" s="2" t="s">
         <v>16</v>
@@ -9698,10 +9689,10 @@
         <v>2024</v>
       </c>
       <c r="B226" s="2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>465</v>
+        <v>478</v>
       </c>
       <c r="D226" s="2" t="s">
         <v>479</v>
@@ -9710,16 +9701,16 @@
         <v>480</v>
       </c>
       <c r="F226" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G226" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H226" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I226" s="2" t="n">
-        <v>54.94</v>
+        <v>53.57</v>
       </c>
       <c r="J226" s="2" t="s">
         <v>16</v>
@@ -9730,7 +9721,7 @@
         <v>2024</v>
       </c>
       <c r="B227" s="2" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C227" s="2" t="s">
         <v>481</v>
@@ -9742,16 +9733,16 @@
         <v>483</v>
       </c>
       <c r="F227" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G227" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H227" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I227" s="2" t="n">
-        <v>53.57</v>
+        <v>53.44</v>
       </c>
       <c r="J227" s="2" t="s">
         <v>16</v>
@@ -9762,28 +9753,28 @@
         <v>2024</v>
       </c>
       <c r="B228" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C228" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="D228" s="2" t="s">
         <v>484</v>
       </c>
-      <c r="D228" s="2" t="s">
+      <c r="E228" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="E228" s="2" t="s">
-        <v>486</v>
-      </c>
       <c r="F228" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G228" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H228" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I228" s="2" t="n">
-        <v>53.44</v>
+        <v>52.23</v>
       </c>
       <c r="J228" s="2" t="s">
         <v>16</v>
@@ -9797,25 +9788,25 @@
         <v>8</v>
       </c>
       <c r="C229" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="D229" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="E229" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="F229" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="D229" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="E229" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="F229" s="2" t="s">
-        <v>468</v>
-      </c>
       <c r="G229" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H229" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I229" s="2" t="n">
-        <v>52.23</v>
+        <v>52.08</v>
       </c>
       <c r="J229" s="2" t="s">
         <v>16</v>
@@ -9829,25 +9820,25 @@
         <v>8</v>
       </c>
       <c r="C230" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="D230" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="E230" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="F230" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="D230" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="E230" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="F230" s="2" t="s">
-        <v>468</v>
-      </c>
       <c r="G230" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H230" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I230" s="2" t="n">
-        <v>52.08</v>
+        <v>51.65</v>
       </c>
       <c r="J230" s="2" t="s">
         <v>16</v>
@@ -9861,25 +9852,25 @@
         <v>8</v>
       </c>
       <c r="C231" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="D231" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="E231" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="F231" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="D231" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="E231" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="F231" s="2" t="s">
-        <v>468</v>
-      </c>
       <c r="G231" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H231" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I231" s="2" t="n">
-        <v>51.65</v>
+        <v>51.36</v>
       </c>
       <c r="J231" s="2" t="s">
         <v>16</v>
@@ -9893,25 +9884,25 @@
         <v>8</v>
       </c>
       <c r="C232" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="D232" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="E232" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="F232" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="D232" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="E232" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="F232" s="2" t="s">
-        <v>468</v>
-      </c>
       <c r="G232" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H232" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I232" s="2" t="n">
-        <v>51.36</v>
+        <v>51.35</v>
       </c>
       <c r="J232" s="2" t="s">
         <v>16</v>
@@ -9925,25 +9916,25 @@
         <v>8</v>
       </c>
       <c r="C233" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="D233" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="E233" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="F233" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="D233" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="E233" s="2" t="s">
-        <v>496</v>
-      </c>
-      <c r="F233" s="2" t="s">
-        <v>468</v>
-      </c>
       <c r="G233" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H233" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I233" s="2" t="n">
-        <v>51.35</v>
+        <v>51.16</v>
       </c>
       <c r="J233" s="2" t="s">
         <v>16</v>
@@ -9957,25 +9948,25 @@
         <v>8</v>
       </c>
       <c r="C234" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="D234" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="E234" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="F234" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="D234" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="E234" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="F234" s="2" t="s">
-        <v>468</v>
-      </c>
       <c r="G234" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H234" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I234" s="2" t="n">
-        <v>51.16</v>
+        <v>50.52</v>
       </c>
       <c r="J234" s="2" t="s">
         <v>16</v>
@@ -9989,25 +9980,25 @@
         <v>8</v>
       </c>
       <c r="C235" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="D235" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="E235" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="F235" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="D235" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="E235" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="F235" s="2" t="s">
-        <v>468</v>
-      </c>
       <c r="G235" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H235" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I235" s="2" t="n">
-        <v>50.52</v>
+        <v>50.47</v>
       </c>
       <c r="J235" s="2" t="s">
         <v>16</v>
@@ -10021,25 +10012,25 @@
         <v>8</v>
       </c>
       <c r="C236" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="D236" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="E236" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="F236" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="D236" s="2" t="s">
-        <v>501</v>
-      </c>
-      <c r="E236" s="2" t="s">
-        <v>502</v>
-      </c>
-      <c r="F236" s="2" t="s">
-        <v>468</v>
-      </c>
       <c r="G236" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H236" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I236" s="2" t="n">
-        <v>50.47</v>
+        <v>50.04</v>
       </c>
       <c r="J236" s="2" t="s">
         <v>16</v>
@@ -10053,25 +10044,25 @@
         <v>8</v>
       </c>
       <c r="C237" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="D237" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="E237" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="F237" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="D237" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="E237" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="F237" s="2" t="s">
-        <v>468</v>
-      </c>
       <c r="G237" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H237" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I237" s="2" t="n">
-        <v>50.04</v>
+        <v>50</v>
       </c>
       <c r="J237" s="2" t="s">
         <v>16</v>
@@ -10085,25 +10076,25 @@
         <v>8</v>
       </c>
       <c r="C238" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="D238" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="E238" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="F238" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="D238" s="2" t="s">
-        <v>505</v>
-      </c>
-      <c r="E238" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="F238" s="2" t="s">
-        <v>468</v>
-      </c>
       <c r="G238" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H238" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I238" s="2" t="n">
-        <v>50</v>
+        <v>49.08</v>
       </c>
       <c r="J238" s="2" t="s">
         <v>16</v>
@@ -10117,25 +10108,25 @@
         <v>8</v>
       </c>
       <c r="C239" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="D239" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="E239" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="F239" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="D239" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="E239" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="F239" s="2" t="s">
-        <v>468</v>
-      </c>
       <c r="G239" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H239" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I239" s="2" t="n">
-        <v>49.08</v>
+        <v>48.7</v>
       </c>
       <c r="J239" s="2" t="s">
         <v>16</v>
@@ -10149,25 +10140,25 @@
         <v>8</v>
       </c>
       <c r="C240" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="D240" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="E240" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="F240" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="D240" s="2" t="s">
-        <v>509</v>
-      </c>
-      <c r="E240" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="F240" s="2" t="s">
-        <v>468</v>
-      </c>
       <c r="G240" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H240" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I240" s="2" t="n">
-        <v>48.7</v>
+        <v>48.44</v>
       </c>
       <c r="J240" s="2" t="s">
         <v>16</v>
@@ -10178,28 +10169,28 @@
         <v>2024</v>
       </c>
       <c r="B241" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C241" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="D241" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="E241" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="F241" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="D241" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="E241" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="F241" s="2" t="s">
-        <v>468</v>
-      </c>
       <c r="G241" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H241" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I241" s="2" t="n">
-        <v>48.44</v>
+        <v>48.41</v>
       </c>
       <c r="J241" s="2" t="s">
         <v>16</v>
@@ -10210,28 +10201,28 @@
         <v>2024</v>
       </c>
       <c r="B242" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="D242" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="E242" s="2" t="s">
         <v>513</v>
       </c>
-      <c r="E242" s="2" t="s">
-        <v>514</v>
-      </c>
       <c r="F242" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G242" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H242" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I242" s="2" t="n">
-        <v>48.41</v>
+        <v>48.38</v>
       </c>
       <c r="J242" s="2" t="s">
         <v>16</v>
@@ -10245,25 +10236,25 @@
         <v>8</v>
       </c>
       <c r="C243" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="D243" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="E243" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="F243" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="D243" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="E243" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="F243" s="2" t="s">
-        <v>468</v>
-      </c>
       <c r="G243" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H243" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I243" s="2" t="n">
-        <v>48.38</v>
+        <v>48.36</v>
       </c>
       <c r="J243" s="2" t="s">
         <v>16</v>
@@ -10274,28 +10265,28 @@
         <v>2024</v>
       </c>
       <c r="B244" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C244" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="D244" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="E244" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="F244" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="D244" s="2" t="s">
-        <v>517</v>
-      </c>
-      <c r="E244" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="F244" s="2" t="s">
-        <v>468</v>
-      </c>
       <c r="G244" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H244" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I244" s="2" t="n">
-        <v>48.36</v>
+        <v>48.25</v>
       </c>
       <c r="J244" s="2" t="s">
         <v>16</v>
@@ -10306,28 +10297,28 @@
         <v>2024</v>
       </c>
       <c r="B245" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="D245" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="E245" s="2" t="s">
         <v>519</v>
       </c>
-      <c r="E245" s="2" t="s">
-        <v>520</v>
-      </c>
       <c r="F245" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G245" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H245" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I245" s="2" t="n">
-        <v>48.25</v>
+        <v>48.12</v>
       </c>
       <c r="J245" s="2" t="s">
         <v>16</v>
@@ -10338,28 +10329,28 @@
         <v>2024</v>
       </c>
       <c r="B246" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>481</v>
+        <v>462</v>
       </c>
       <c r="D246" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="E246" s="2" t="s">
         <v>521</v>
       </c>
-      <c r="E246" s="2" t="s">
-        <v>522</v>
-      </c>
       <c r="F246" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G246" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H246" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I246" s="2" t="n">
-        <v>48.12</v>
+        <v>47.91</v>
       </c>
       <c r="J246" s="2" t="s">
         <v>16</v>
@@ -10370,28 +10361,28 @@
         <v>2024</v>
       </c>
       <c r="B247" s="2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C247" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="D247" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="E247" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="F247" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="D247" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="E247" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="F247" s="2" t="s">
-        <v>468</v>
-      </c>
       <c r="G247" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H247" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I247" s="2" t="n">
-        <v>47.91</v>
+        <v>47.73</v>
       </c>
       <c r="J247" s="2" t="s">
         <v>16</v>
@@ -10402,28 +10393,28 @@
         <v>2024</v>
       </c>
       <c r="B248" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>481</v>
+        <v>462</v>
       </c>
       <c r="D248" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="E248" s="2" t="s">
         <v>525</v>
       </c>
-      <c r="E248" s="2" t="s">
-        <v>526</v>
-      </c>
       <c r="F248" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G248" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H248" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I248" s="2" t="n">
-        <v>47.73</v>
+        <v>46.65</v>
       </c>
       <c r="J248" s="2" t="s">
         <v>16</v>
@@ -10437,25 +10428,25 @@
         <v>8</v>
       </c>
       <c r="C249" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="D249" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="E249" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="F249" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="D249" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="E249" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="F249" s="2" t="s">
-        <v>468</v>
-      </c>
       <c r="G249" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H249" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I249" s="2" t="n">
-        <v>46.65</v>
+        <v>46.63</v>
       </c>
       <c r="J249" s="2" t="s">
         <v>16</v>
@@ -10469,25 +10460,25 @@
         <v>8</v>
       </c>
       <c r="C250" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="D250" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="E250" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="F250" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="D250" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="E250" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="F250" s="2" t="s">
-        <v>468</v>
-      </c>
       <c r="G250" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H250" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I250" s="2" t="n">
-        <v>46.63</v>
+        <v>46.48</v>
       </c>
       <c r="J250" s="2" t="s">
         <v>16</v>
@@ -10498,28 +10489,28 @@
         <v>2024</v>
       </c>
       <c r="B251" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C251" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="D251" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="E251" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="F251" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="D251" s="2" t="s">
-        <v>531</v>
-      </c>
-      <c r="E251" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="F251" s="2" t="s">
-        <v>468</v>
-      </c>
       <c r="G251" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H251" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I251" s="2" t="n">
-        <v>46.48</v>
+        <v>46.32</v>
       </c>
       <c r="J251" s="2" t="s">
         <v>16</v>
@@ -10533,25 +10524,25 @@
         <v>9</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="D252" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="E252" s="2" t="s">
         <v>533</v>
       </c>
-      <c r="E252" s="2" t="s">
-        <v>534</v>
-      </c>
       <c r="F252" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G252" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H252" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I252" s="2" t="n">
-        <v>46.32</v>
+        <v>46.07</v>
       </c>
       <c r="J252" s="2" t="s">
         <v>16</v>
@@ -10562,28 +10553,28 @@
         <v>2024</v>
       </c>
       <c r="B253" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="D253" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="E253" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="E253" s="2" t="s">
-        <v>536</v>
-      </c>
       <c r="F253" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G253" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H253" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I253" s="2" t="n">
-        <v>46.07</v>
+        <v>46.02</v>
       </c>
       <c r="J253" s="2" t="s">
         <v>16</v>
@@ -10597,25 +10588,25 @@
         <v>10</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="D254" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="E254" s="2" t="s">
         <v>537</v>
       </c>
-      <c r="E254" s="2" t="s">
-        <v>538</v>
-      </c>
       <c r="F254" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G254" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H254" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I254" s="2" t="n">
-        <v>46.02</v>
+        <v>45.86</v>
       </c>
       <c r="J254" s="2" t="s">
         <v>16</v>
@@ -10626,28 +10617,28 @@
         <v>2024</v>
       </c>
       <c r="B255" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="D255" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="E255" s="2" t="s">
         <v>539</v>
       </c>
-      <c r="E255" s="2" t="s">
-        <v>540</v>
-      </c>
       <c r="F255" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G255" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H255" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I255" s="2" t="n">
-        <v>45.86</v>
+        <v>45.71</v>
       </c>
       <c r="J255" s="2" t="s">
         <v>16</v>
@@ -10661,25 +10652,25 @@
         <v>8</v>
       </c>
       <c r="C256" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="D256" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="E256" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="F256" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="D256" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="E256" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="F256" s="2" t="s">
-        <v>468</v>
-      </c>
       <c r="G256" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H256" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I256" s="2" t="n">
-        <v>45.71</v>
+        <v>45.53</v>
       </c>
       <c r="J256" s="2" t="s">
         <v>16</v>
@@ -10690,28 +10681,28 @@
         <v>2024</v>
       </c>
       <c r="B257" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C257" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="D257" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="E257" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="F257" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="D257" s="2" t="s">
-        <v>543</v>
-      </c>
-      <c r="E257" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="F257" s="2" t="s">
-        <v>468</v>
-      </c>
       <c r="G257" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H257" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I257" s="2" t="n">
-        <v>45.53</v>
+        <v>45.37</v>
       </c>
       <c r="J257" s="2" t="s">
         <v>16</v>
@@ -10725,25 +10716,25 @@
         <v>10</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="D258" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="E258" s="2" t="s">
         <v>545</v>
       </c>
-      <c r="E258" s="2" t="s">
-        <v>546</v>
-      </c>
       <c r="F258" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G258" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H258" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I258" s="2" t="n">
-        <v>45.37</v>
+        <v>45.26</v>
       </c>
       <c r="J258" s="2" t="s">
         <v>16</v>
@@ -10754,28 +10745,28 @@
         <v>2024</v>
       </c>
       <c r="B259" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="D259" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="E259" s="2" t="s">
         <v>547</v>
       </c>
-      <c r="E259" s="2" t="s">
-        <v>548</v>
-      </c>
       <c r="F259" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G259" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H259" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I259" s="2" t="n">
-        <v>45.26</v>
+        <v>45.24</v>
       </c>
       <c r="J259" s="2" t="s">
         <v>16</v>
@@ -10789,25 +10780,25 @@
         <v>9</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="D260" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="E260" s="2" t="s">
         <v>549</v>
       </c>
-      <c r="E260" s="2" t="s">
-        <v>550</v>
-      </c>
       <c r="F260" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G260" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H260" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I260" s="2" t="n">
-        <v>45.24</v>
+        <v>45.2</v>
       </c>
       <c r="J260" s="2" t="s">
         <v>16</v>
@@ -10818,28 +10809,28 @@
         <v>2024</v>
       </c>
       <c r="B261" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>484</v>
+        <v>462</v>
       </c>
       <c r="D261" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="E261" s="2" t="s">
         <v>551</v>
       </c>
-      <c r="E261" s="2" t="s">
-        <v>552</v>
-      </c>
       <c r="F261" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G261" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H261" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I261" s="2" t="n">
-        <v>45.2</v>
+        <v>44.79</v>
       </c>
       <c r="J261" s="2" t="s">
         <v>16</v>
@@ -10850,28 +10841,28 @@
         <v>2024</v>
       </c>
       <c r="B262" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C262" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="D262" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="E262" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="F262" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="D262" s="2" t="s">
-        <v>553</v>
-      </c>
-      <c r="E262" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="F262" s="2" t="s">
-        <v>468</v>
-      </c>
       <c r="G262" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H262" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I262" s="2" t="n">
-        <v>44.79</v>
+        <v>44.67</v>
       </c>
       <c r="J262" s="2" t="s">
         <v>16</v>
@@ -10885,25 +10876,25 @@
         <v>10</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="D263" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="E263" s="2" t="s">
         <v>555</v>
       </c>
-      <c r="E263" s="2" t="s">
-        <v>556</v>
-      </c>
       <c r="F263" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G263" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H263" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I263" s="2" t="n">
-        <v>44.67</v>
+        <v>44.57</v>
       </c>
       <c r="J263" s="2" t="s">
         <v>16</v>
@@ -10914,28 +10905,28 @@
         <v>2024</v>
       </c>
       <c r="B264" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="D264" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="E264" s="2" t="s">
         <v>557</v>
       </c>
-      <c r="E264" s="2" t="s">
-        <v>558</v>
-      </c>
       <c r="F264" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G264" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H264" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I264" s="2" t="n">
-        <v>44.57</v>
+        <v>44.41</v>
       </c>
       <c r="J264" s="2" t="s">
         <v>16</v>
@@ -10946,28 +10937,28 @@
         <v>2024</v>
       </c>
       <c r="B265" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C265" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="D265" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="E265" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="F265" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="D265" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="E265" s="2" t="s">
-        <v>560</v>
-      </c>
-      <c r="F265" s="2" t="s">
-        <v>468</v>
-      </c>
       <c r="G265" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H265" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I265" s="2" t="n">
-        <v>44.41</v>
+        <v>44.22</v>
       </c>
       <c r="J265" s="2" t="s">
         <v>16</v>
@@ -10981,25 +10972,25 @@
         <v>9</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="D266" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="E266" s="2" t="s">
         <v>561</v>
       </c>
-      <c r="E266" s="2" t="s">
-        <v>562</v>
-      </c>
       <c r="F266" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G266" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H266" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I266" s="2" t="n">
-        <v>44.22</v>
+        <v>44.18</v>
       </c>
       <c r="J266" s="2" t="s">
         <v>16</v>
@@ -11013,25 +11004,25 @@
         <v>9</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="D267" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="E267" s="2" t="s">
         <v>563</v>
       </c>
-      <c r="E267" s="2" t="s">
-        <v>564</v>
-      </c>
       <c r="F267" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G267" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H267" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I267" s="2" t="n">
-        <v>44.18</v>
+        <v>44.03</v>
       </c>
       <c r="J267" s="2" t="s">
         <v>16</v>
@@ -11042,28 +11033,28 @@
         <v>2024</v>
       </c>
       <c r="B268" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="D268" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="E268" s="2" t="s">
         <v>565</v>
       </c>
-      <c r="E268" s="2" t="s">
-        <v>566</v>
-      </c>
       <c r="F268" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G268" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H268" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I268" s="2" t="n">
-        <v>44.03</v>
+        <v>43.64</v>
       </c>
       <c r="J268" s="2" t="s">
         <v>16</v>
@@ -11074,28 +11065,28 @@
         <v>2024</v>
       </c>
       <c r="B269" s="2" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C269" s="2" t="s">
         <v>481</v>
       </c>
       <c r="D269" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="E269" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="E269" s="2" t="s">
-        <v>568</v>
-      </c>
       <c r="F269" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G269" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H269" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I269" s="2" t="n">
-        <v>43.64</v>
+        <v>43.55</v>
       </c>
       <c r="J269" s="2" t="s">
         <v>16</v>
@@ -11109,25 +11100,25 @@
         <v>9</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="D270" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="E270" s="2" t="s">
         <v>569</v>
       </c>
-      <c r="E270" s="2" t="s">
-        <v>570</v>
-      </c>
       <c r="F270" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G270" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H270" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I270" s="2" t="n">
-        <v>43.55</v>
+        <v>43.41</v>
       </c>
       <c r="J270" s="2" t="s">
         <v>16</v>
@@ -11138,28 +11129,28 @@
         <v>2024</v>
       </c>
       <c r="B271" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="D271" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="E271" s="2" t="s">
         <v>571</v>
       </c>
-      <c r="E271" s="2" t="s">
-        <v>572</v>
-      </c>
       <c r="F271" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G271" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H271" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I271" s="2" t="n">
-        <v>43.41</v>
+        <v>43.28</v>
       </c>
       <c r="J271" s="2" t="s">
         <v>16</v>
@@ -11170,28 +11161,28 @@
         <v>2024</v>
       </c>
       <c r="B272" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="D272" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="E272" s="2" t="s">
         <v>573</v>
       </c>
-      <c r="E272" s="2" t="s">
-        <v>574</v>
-      </c>
       <c r="F272" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G272" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H272" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I272" s="2" t="n">
-        <v>43.28</v>
+        <v>43.15</v>
       </c>
       <c r="J272" s="2" t="s">
         <v>16</v>
@@ -11202,28 +11193,28 @@
         <v>2024</v>
       </c>
       <c r="B273" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C273" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="D273" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="E273" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="F273" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="D273" s="2" t="s">
-        <v>575</v>
-      </c>
-      <c r="E273" s="2" t="s">
-        <v>576</v>
-      </c>
-      <c r="F273" s="2" t="s">
-        <v>468</v>
-      </c>
       <c r="G273" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H273" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I273" s="2" t="n">
-        <v>43.15</v>
+        <v>42.97</v>
       </c>
       <c r="J273" s="2" t="s">
         <v>16</v>
@@ -11237,25 +11228,25 @@
         <v>9</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="D274" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="E274" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="E274" s="2" t="s">
-        <v>578</v>
-      </c>
       <c r="F274" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G274" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H274" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I274" s="2" t="n">
-        <v>42.97</v>
+        <v>42.65</v>
       </c>
       <c r="J274" s="2" t="s">
         <v>16</v>
@@ -11266,28 +11257,28 @@
         <v>2024</v>
       </c>
       <c r="B275" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="D275" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="E275" s="2" t="s">
         <v>579</v>
       </c>
-      <c r="E275" s="2" t="s">
-        <v>580</v>
-      </c>
       <c r="F275" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G275" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H275" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I275" s="2" t="n">
-        <v>42.65</v>
+        <v>42.64</v>
       </c>
       <c r="J275" s="2" t="s">
         <v>16</v>
@@ -11298,28 +11289,28 @@
         <v>2024</v>
       </c>
       <c r="B276" s="2" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C276" s="2" t="s">
         <v>481</v>
       </c>
       <c r="D276" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="E276" s="2" t="s">
         <v>581</v>
       </c>
-      <c r="E276" s="2" t="s">
-        <v>582</v>
-      </c>
       <c r="F276" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G276" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H276" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I276" s="2" t="n">
-        <v>42.64</v>
+        <v>42.61</v>
       </c>
       <c r="J276" s="2" t="s">
         <v>16</v>
@@ -11330,28 +11321,28 @@
         <v>2024</v>
       </c>
       <c r="B277" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>484</v>
+        <v>462</v>
       </c>
       <c r="D277" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="E277" s="2" t="s">
         <v>583</v>
       </c>
-      <c r="E277" s="2" t="s">
-        <v>584</v>
-      </c>
       <c r="F277" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G277" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H277" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I277" s="2" t="n">
-        <v>42.61</v>
+        <v>42.38</v>
       </c>
       <c r="J277" s="2" t="s">
         <v>16</v>
@@ -11365,25 +11356,25 @@
         <v>8</v>
       </c>
       <c r="C278" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="D278" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="E278" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="F278" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="D278" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="E278" s="2" t="s">
-        <v>586</v>
-      </c>
-      <c r="F278" s="2" t="s">
-        <v>468</v>
-      </c>
       <c r="G278" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H278" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I278" s="2" t="n">
-        <v>42.38</v>
+        <v>42.35</v>
       </c>
       <c r="J278" s="2" t="s">
         <v>16</v>
@@ -11394,28 +11385,28 @@
         <v>2024</v>
       </c>
       <c r="B279" s="2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C279" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="D279" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="E279" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="F279" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="D279" s="2" t="s">
-        <v>587</v>
-      </c>
-      <c r="E279" s="2" t="s">
-        <v>588</v>
-      </c>
-      <c r="F279" s="2" t="s">
-        <v>468</v>
-      </c>
       <c r="G279" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H279" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I279" s="2" t="n">
-        <v>42.35</v>
+        <v>42.33</v>
       </c>
       <c r="J279" s="2" t="s">
         <v>16</v>
@@ -11426,28 +11417,28 @@
         <v>2024</v>
       </c>
       <c r="B280" s="2" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C280" s="2" t="s">
         <v>481</v>
       </c>
       <c r="D280" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="E280" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="E280" s="2" t="s">
-        <v>590</v>
-      </c>
       <c r="F280" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G280" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H280" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I280" s="2" t="n">
-        <v>42.33</v>
+        <v>42.27</v>
       </c>
       <c r="J280" s="2" t="s">
         <v>16</v>
@@ -11458,28 +11449,28 @@
         <v>2024</v>
       </c>
       <c r="B281" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="D281" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="E281" s="2" t="s">
         <v>591</v>
       </c>
-      <c r="E281" s="2" t="s">
-        <v>592</v>
-      </c>
       <c r="F281" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G281" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H281" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I281" s="2" t="n">
-        <v>42.27</v>
+        <v>42.12</v>
       </c>
       <c r="J281" s="2" t="s">
         <v>16</v>
@@ -11490,28 +11481,28 @@
         <v>2024</v>
       </c>
       <c r="B282" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="D282" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="E282" s="2" t="s">
         <v>593</v>
       </c>
-      <c r="E282" s="2" t="s">
-        <v>594</v>
-      </c>
       <c r="F282" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G282" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H282" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I282" s="2" t="n">
-        <v>42.12</v>
+        <v>42.09</v>
       </c>
       <c r="J282" s="2" t="s">
         <v>16</v>
@@ -11525,25 +11516,25 @@
         <v>9</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="D283" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="E283" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="E283" s="2" t="s">
-        <v>596</v>
-      </c>
       <c r="F283" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G283" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H283" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I283" s="2" t="n">
-        <v>42.09</v>
+        <v>41.57</v>
       </c>
       <c r="J283" s="2" t="s">
         <v>16</v>
@@ -11557,25 +11548,25 @@
         <v>9</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="D284" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="E284" s="2" t="s">
         <v>597</v>
       </c>
-      <c r="E284" s="2" t="s">
-        <v>598</v>
-      </c>
       <c r="F284" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G284" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H284" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I284" s="2" t="n">
-        <v>41.57</v>
+        <v>41.46</v>
       </c>
       <c r="J284" s="2" t="s">
         <v>16</v>
@@ -11589,25 +11580,25 @@
         <v>9</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="D285" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="E285" s="2" t="s">
         <v>599</v>
       </c>
-      <c r="E285" s="2" t="s">
-        <v>600</v>
-      </c>
       <c r="F285" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G285" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H285" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I285" s="2" t="n">
-        <v>41.46</v>
+        <v>41.24</v>
       </c>
       <c r="J285" s="2" t="s">
         <v>16</v>
@@ -11618,28 +11609,28 @@
         <v>2024</v>
       </c>
       <c r="B286" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="D286" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="E286" s="2" t="s">
         <v>601</v>
       </c>
-      <c r="E286" s="2" t="s">
-        <v>602</v>
-      </c>
       <c r="F286" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G286" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H286" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I286" s="2" t="n">
-        <v>41.24</v>
+        <v>41.2</v>
       </c>
       <c r="J286" s="2" t="s">
         <v>16</v>
@@ -11650,28 +11641,28 @@
         <v>2024</v>
       </c>
       <c r="B287" s="2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="D287" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="E287" s="2" t="s">
         <v>603</v>
       </c>
-      <c r="E287" s="2" t="s">
-        <v>604</v>
-      </c>
       <c r="F287" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G287" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H287" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I287" s="2" t="n">
-        <v>41.2</v>
+        <v>41.17</v>
       </c>
       <c r="J287" s="2" t="s">
         <v>16</v>
@@ -11685,25 +11676,25 @@
         <v>10</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="D288" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="E288" s="2" t="s">
         <v>605</v>
       </c>
-      <c r="E288" s="2" t="s">
-        <v>606</v>
-      </c>
       <c r="F288" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G288" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H288" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I288" s="2" t="n">
-        <v>41.17</v>
+        <v>41.08</v>
       </c>
       <c r="J288" s="2" t="s">
         <v>16</v>
@@ -11714,28 +11705,28 @@
         <v>2024</v>
       </c>
       <c r="B289" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="D289" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="E289" s="2" t="s">
         <v>607</v>
       </c>
-      <c r="E289" s="2" t="s">
-        <v>608</v>
-      </c>
       <c r="F289" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G289" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H289" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I289" s="2" t="n">
-        <v>41.08</v>
+        <v>41.07</v>
       </c>
       <c r="J289" s="2" t="s">
         <v>16</v>
@@ -11746,22 +11737,22 @@
         <v>2024</v>
       </c>
       <c r="B290" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="D290" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="E290" s="2" t="s">
         <v>609</v>
       </c>
-      <c r="E290" s="2" t="s">
-        <v>610</v>
-      </c>
       <c r="F290" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G290" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H290" s="2" t="s">
         <v>15</v>
@@ -11778,28 +11769,28 @@
         <v>2024</v>
       </c>
       <c r="B291" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="D291" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="E291" s="2" t="s">
         <v>611</v>
       </c>
-      <c r="E291" s="2" t="s">
-        <v>612</v>
-      </c>
       <c r="F291" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G291" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H291" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I291" s="2" t="n">
-        <v>41.07</v>
+        <v>40.99</v>
       </c>
       <c r="J291" s="2" t="s">
         <v>16</v>
@@ -11810,28 +11801,28 @@
         <v>2024</v>
       </c>
       <c r="B292" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="D292" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="E292" s="2" t="s">
         <v>613</v>
       </c>
-      <c r="E292" s="2" t="s">
-        <v>614</v>
-      </c>
       <c r="F292" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G292" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H292" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I292" s="2" t="n">
-        <v>40.99</v>
+        <v>40.94</v>
       </c>
       <c r="J292" s="2" t="s">
         <v>16</v>
@@ -11842,28 +11833,28 @@
         <v>2024</v>
       </c>
       <c r="B293" s="2" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C293" s="2" t="s">
         <v>481</v>
       </c>
       <c r="D293" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="E293" s="2" t="s">
         <v>615</v>
       </c>
-      <c r="E293" s="2" t="s">
-        <v>616</v>
-      </c>
       <c r="F293" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G293" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H293" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I293" s="2" t="n">
-        <v>40.94</v>
+        <v>40.67</v>
       </c>
       <c r="J293" s="2" t="s">
         <v>16</v>
@@ -11877,19 +11868,19 @@
         <v>9</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="D294" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="E294" s="2" t="s">
         <v>617</v>
       </c>
-      <c r="E294" s="2" t="s">
-        <v>618</v>
-      </c>
       <c r="F294" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G294" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H294" s="2" t="s">
         <v>15</v>
@@ -11909,25 +11900,25 @@
         <v>9</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="D295" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="E295" s="2" t="s">
         <v>619</v>
       </c>
-      <c r="E295" s="2" t="s">
-        <v>620</v>
-      </c>
       <c r="F295" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G295" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H295" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I295" s="2" t="n">
-        <v>40.67</v>
+        <v>40.63</v>
       </c>
       <c r="J295" s="2" t="s">
         <v>16</v>
@@ -11938,28 +11929,28 @@
         <v>2024</v>
       </c>
       <c r="B296" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="D296" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="E296" s="2" t="s">
         <v>621</v>
       </c>
-      <c r="E296" s="2" t="s">
-        <v>622</v>
-      </c>
       <c r="F296" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G296" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H296" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I296" s="2" t="n">
-        <v>40.63</v>
+        <v>40.39</v>
       </c>
       <c r="J296" s="2" t="s">
         <v>16</v>
@@ -11973,25 +11964,25 @@
         <v>14</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="D297" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="E297" s="2" t="s">
         <v>623</v>
       </c>
-      <c r="E297" s="2" t="s">
-        <v>624</v>
-      </c>
       <c r="F297" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G297" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H297" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I297" s="2" t="n">
-        <v>40.39</v>
+        <v>40.25</v>
       </c>
       <c r="J297" s="2" t="s">
         <v>16</v>
@@ -12005,25 +11996,25 @@
         <v>14</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="D298" s="2" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="E298" s="2" t="s">
-        <v>626</v>
+        <v>473</v>
       </c>
       <c r="F298" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G298" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H298" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I298" s="2" t="n">
-        <v>40.25</v>
+        <v>39.86</v>
       </c>
       <c r="J298" s="2" t="s">
         <v>16</v>
@@ -12034,28 +12025,28 @@
         <v>2024</v>
       </c>
       <c r="B299" s="2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="D299" s="2" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="E299" s="2" t="s">
-        <v>476</v>
+        <v>626</v>
       </c>
       <c r="F299" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G299" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H299" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I299" s="2" t="n">
-        <v>39.86</v>
+        <v>39.56</v>
       </c>
       <c r="J299" s="2" t="s">
         <v>16</v>
@@ -12066,28 +12057,28 @@
         <v>2024</v>
       </c>
       <c r="B300" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="D300" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="E300" s="2" t="s">
         <v>628</v>
       </c>
-      <c r="E300" s="2" t="s">
-        <v>629</v>
-      </c>
       <c r="F300" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G300" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H300" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I300" s="2" t="n">
-        <v>39.56</v>
+        <v>39.47</v>
       </c>
       <c r="J300" s="2" t="s">
         <v>16</v>
@@ -12098,28 +12089,28 @@
         <v>2024</v>
       </c>
       <c r="B301" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="D301" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="E301" s="2" t="s">
         <v>630</v>
       </c>
-      <c r="E301" s="2" t="s">
-        <v>631</v>
-      </c>
       <c r="F301" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G301" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H301" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I301" s="2" t="n">
-        <v>39.47</v>
+        <v>39.44</v>
       </c>
       <c r="J301" s="2" t="s">
         <v>16</v>
@@ -12130,28 +12121,28 @@
         <v>2024</v>
       </c>
       <c r="B302" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="D302" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="E302" s="2" t="s">
         <v>632</v>
       </c>
-      <c r="E302" s="2" t="s">
-        <v>633</v>
-      </c>
       <c r="F302" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G302" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H302" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I302" s="2" t="n">
-        <v>39.44</v>
+        <v>39.32</v>
       </c>
       <c r="J302" s="2" t="s">
         <v>16</v>
@@ -12162,28 +12153,28 @@
         <v>2024</v>
       </c>
       <c r="B303" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C303" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="D303" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="E303" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="F303" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="D303" s="2" t="s">
-        <v>634</v>
-      </c>
-      <c r="E303" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="F303" s="2" t="s">
-        <v>468</v>
-      </c>
       <c r="G303" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H303" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I303" s="2" t="n">
-        <v>39.32</v>
+        <v>39.12</v>
       </c>
       <c r="J303" s="2" t="s">
         <v>16</v>
@@ -12197,25 +12188,25 @@
         <v>10</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="D304" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="E304" s="2" t="s">
         <v>636</v>
       </c>
-      <c r="E304" s="2" t="s">
-        <v>637</v>
-      </c>
       <c r="F304" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G304" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H304" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I304" s="2" t="n">
-        <v>39.12</v>
+        <v>38.97</v>
       </c>
       <c r="J304" s="2" t="s">
         <v>16</v>
@@ -12229,25 +12220,25 @@
         <v>10</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="D305" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="E305" s="2" t="s">
         <v>638</v>
       </c>
-      <c r="E305" s="2" t="s">
-        <v>639</v>
-      </c>
       <c r="F305" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G305" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H305" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I305" s="2" t="n">
-        <v>38.97</v>
+        <v>38.93</v>
       </c>
       <c r="J305" s="2" t="s">
         <v>16</v>
@@ -12258,28 +12249,28 @@
         <v>2024</v>
       </c>
       <c r="B306" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="D306" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="E306" s="2" t="s">
         <v>640</v>
       </c>
-      <c r="E306" s="2" t="s">
-        <v>641</v>
-      </c>
       <c r="F306" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G306" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H306" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I306" s="2" t="n">
-        <v>38.93</v>
+        <v>38.81</v>
       </c>
       <c r="J306" s="2" t="s">
         <v>16</v>
@@ -12290,28 +12281,28 @@
         <v>2024</v>
       </c>
       <c r="B307" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="D307" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="E307" s="2" t="s">
         <v>642</v>
       </c>
-      <c r="E307" s="2" t="s">
-        <v>643</v>
-      </c>
       <c r="F307" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G307" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H307" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I307" s="2" t="n">
-        <v>38.81</v>
+        <v>38.74</v>
       </c>
       <c r="J307" s="2" t="s">
         <v>16</v>
@@ -12325,25 +12316,25 @@
         <v>10</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="D308" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="E308" s="2" t="s">
         <v>644</v>
       </c>
-      <c r="E308" s="2" t="s">
-        <v>645</v>
-      </c>
       <c r="F308" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G308" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H308" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I308" s="2" t="n">
-        <v>38.74</v>
+        <v>38.71</v>
       </c>
       <c r="J308" s="2" t="s">
         <v>16</v>
@@ -12354,28 +12345,28 @@
         <v>2024</v>
       </c>
       <c r="B309" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C309" s="2" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="D309" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="E309" s="2" t="s">
         <v>646</v>
       </c>
-      <c r="E309" s="2" t="s">
-        <v>647</v>
-      </c>
       <c r="F309" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G309" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H309" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I309" s="2" t="n">
-        <v>38.71</v>
+        <v>38.7</v>
       </c>
       <c r="J309" s="2" t="s">
         <v>16</v>
@@ -12386,28 +12377,28 @@
         <v>2024</v>
       </c>
       <c r="B310" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C310" s="2" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="D310" s="2" t="s">
+        <v>647</v>
+      </c>
+      <c r="E310" s="2" t="s">
         <v>648</v>
       </c>
-      <c r="E310" s="2" t="s">
-        <v>649</v>
-      </c>
       <c r="F310" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G310" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H310" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I310" s="2" t="n">
-        <v>38.7</v>
+        <v>37.94</v>
       </c>
       <c r="J310" s="2" t="s">
         <v>16</v>
@@ -12418,28 +12409,28 @@
         <v>2024</v>
       </c>
       <c r="B311" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C311" s="2" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="D311" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="E311" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="E311" s="2" t="s">
-        <v>651</v>
-      </c>
       <c r="F311" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G311" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H311" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I311" s="2" t="n">
-        <v>37.94</v>
+        <v>37.36</v>
       </c>
       <c r="J311" s="2" t="s">
         <v>16</v>
@@ -12450,28 +12441,28 @@
         <v>2024</v>
       </c>
       <c r="B312" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C312" s="2" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="D312" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="E312" s="2" t="s">
         <v>652</v>
       </c>
-      <c r="E312" s="2" t="s">
-        <v>653</v>
-      </c>
       <c r="F312" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G312" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H312" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I312" s="2" t="n">
-        <v>37.36</v>
+        <v>37.23</v>
       </c>
       <c r="J312" s="2" t="s">
         <v>16</v>
@@ -12485,25 +12476,25 @@
         <v>10</v>
       </c>
       <c r="C313" s="2" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="D313" s="2" t="s">
+        <v>653</v>
+      </c>
+      <c r="E313" s="2" t="s">
         <v>654</v>
       </c>
-      <c r="E313" s="2" t="s">
-        <v>655</v>
-      </c>
       <c r="F313" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G313" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H313" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I313" s="2" t="n">
-        <v>37.23</v>
+        <v>37.07</v>
       </c>
       <c r="J313" s="2" t="s">
         <v>16</v>
@@ -12514,28 +12505,28 @@
         <v>2024</v>
       </c>
       <c r="B314" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C314" s="2" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="D314" s="2" t="s">
+        <v>655</v>
+      </c>
+      <c r="E314" s="2" t="s">
         <v>656</v>
       </c>
-      <c r="E314" s="2" t="s">
-        <v>657</v>
-      </c>
       <c r="F314" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G314" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H314" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I314" s="2" t="n">
-        <v>37.07</v>
+        <v>35.94</v>
       </c>
       <c r="J314" s="2" t="s">
         <v>16</v>
@@ -12546,28 +12537,28 @@
         <v>2024</v>
       </c>
       <c r="B315" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C315" s="2" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="D315" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="E315" s="2" t="s">
         <v>658</v>
       </c>
-      <c r="E315" s="2" t="s">
-        <v>659</v>
-      </c>
       <c r="F315" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G315" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H315" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I315" s="2" t="n">
-        <v>35.94</v>
+        <v>35.85</v>
       </c>
       <c r="J315" s="2" t="s">
         <v>16</v>
@@ -12581,25 +12572,25 @@
         <v>10</v>
       </c>
       <c r="C316" s="2" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="D316" s="2" t="s">
+        <v>659</v>
+      </c>
+      <c r="E316" s="2" t="s">
         <v>660</v>
       </c>
-      <c r="E316" s="2" t="s">
-        <v>661</v>
-      </c>
       <c r="F316" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G316" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H316" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I316" s="2" t="n">
-        <v>35.85</v>
+        <v>35.63</v>
       </c>
       <c r="J316" s="2" t="s">
         <v>16</v>
@@ -12613,25 +12604,25 @@
         <v>10</v>
       </c>
       <c r="C317" s="2" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="D317" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="E317" s="2" t="s">
         <v>662</v>
       </c>
-      <c r="E317" s="2" t="s">
-        <v>663</v>
-      </c>
       <c r="F317" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G317" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H317" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I317" s="2" t="n">
-        <v>35.63</v>
+        <v>35.41</v>
       </c>
       <c r="J317" s="2" t="s">
         <v>16</v>
@@ -12642,28 +12633,28 @@
         <v>2024</v>
       </c>
       <c r="B318" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="D318" s="2" t="s">
+        <v>663</v>
+      </c>
+      <c r="E318" s="2" t="s">
         <v>664</v>
       </c>
-      <c r="E318" s="2" t="s">
-        <v>665</v>
-      </c>
       <c r="F318" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G318" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H318" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I318" s="2" t="n">
-        <v>35.41</v>
+        <v>35.4</v>
       </c>
       <c r="J318" s="2" t="s">
         <v>16</v>
@@ -12677,25 +12668,25 @@
         <v>9</v>
       </c>
       <c r="C319" s="2" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="D319" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="E319" s="2" t="s">
         <v>666</v>
       </c>
-      <c r="E319" s="2" t="s">
-        <v>667</v>
-      </c>
       <c r="F319" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G319" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H319" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I319" s="2" t="n">
-        <v>35.4</v>
+        <v>34.14</v>
       </c>
       <c r="J319" s="2" t="s">
         <v>16</v>
@@ -12706,28 +12697,28 @@
         <v>2024</v>
       </c>
       <c r="B320" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C320" s="2" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="D320" s="2" t="s">
+        <v>667</v>
+      </c>
+      <c r="E320" s="2" t="s">
         <v>668</v>
       </c>
-      <c r="E320" s="2" t="s">
-        <v>669</v>
-      </c>
       <c r="F320" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G320" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H320" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I320" s="2" t="n">
-        <v>34.14</v>
+        <v>33.95</v>
       </c>
       <c r="J320" s="2" t="s">
         <v>16</v>
@@ -12741,25 +12732,25 @@
         <v>10</v>
       </c>
       <c r="C321" s="2" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="D321" s="2" t="s">
+        <v>669</v>
+      </c>
+      <c r="E321" s="2" t="s">
         <v>670</v>
       </c>
-      <c r="E321" s="2" t="s">
-        <v>671</v>
-      </c>
       <c r="F321" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G321" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H321" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I321" s="2" t="n">
-        <v>33.95</v>
+        <v>33.18</v>
       </c>
       <c r="J321" s="2" t="s">
         <v>16</v>
@@ -12770,28 +12761,28 @@
         <v>2024</v>
       </c>
       <c r="B322" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C322" s="2" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="D322" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="E322" s="2" t="s">
         <v>672</v>
       </c>
-      <c r="E322" s="2" t="s">
-        <v>673</v>
-      </c>
       <c r="F322" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G322" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H322" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I322" s="2" t="n">
-        <v>33.18</v>
+        <v>31.28</v>
       </c>
       <c r="J322" s="2" t="s">
         <v>16</v>
@@ -12802,22 +12793,22 @@
         <v>2024</v>
       </c>
       <c r="B323" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="D323" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="E323" s="2" t="s">
         <v>674</v>
       </c>
-      <c r="E323" s="2" t="s">
-        <v>675</v>
-      </c>
       <c r="F323" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G323" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H323" s="2" t="s">
         <v>15</v>
@@ -12834,28 +12825,28 @@
         <v>2024</v>
       </c>
       <c r="B324" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C324" s="2" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="D324" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="E324" s="2" t="s">
         <v>676</v>
       </c>
-      <c r="E324" s="2" t="s">
-        <v>677</v>
-      </c>
       <c r="F324" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G324" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H324" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I324" s="2" t="n">
-        <v>31.28</v>
+        <v>29.01</v>
       </c>
       <c r="J324" s="2" t="s">
         <v>16</v>
@@ -12866,67 +12857,35 @@
         <v>2024</v>
       </c>
       <c r="B325" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C325" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="D325" s="2" t="s">
+        <v>677</v>
+      </c>
+      <c r="E325" s="2" t="s">
+        <v>678</v>
+      </c>
+      <c r="F325" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="D325" s="2" t="s">
-        <v>678</v>
-      </c>
-      <c r="E325" s="2" t="s">
-        <v>679</v>
-      </c>
-      <c r="F325" s="2" t="s">
-        <v>468</v>
-      </c>
       <c r="G325" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H325" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I325" s="2" t="n">
-        <v>29.01</v>
+        <v>26.46</v>
       </c>
       <c r="J325" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="326">
-      <c r="A326" s="2" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B326" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="C326" s="2" t="s">
-        <v>484</v>
-      </c>
-      <c r="D326" s="2" t="s">
-        <v>680</v>
-      </c>
-      <c r="E326" s="2" t="s">
-        <v>681</v>
-      </c>
-      <c r="F326" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="G326" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="H326" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I326" s="2" t="n">
-        <v>26.46</v>
-      </c>
-      <c r="J326" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J326"/>
+  <autoFilter ref="A1:J325"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -12943,7 +12902,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>8</v>
@@ -12951,50 +12910,50 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
     </row>
   </sheetData>
@@ -13016,21 +12975,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>15</v>
@@ -13039,7 +12998,7 @@
         <v>2024</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_nacionales/plot_nacional_e_supneta_a_2024.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_supneta_a_2024.xlsx
@@ -2062,7 +2062,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 12:55</t>
+    <t xml:space="preserve">2026-09-08 10:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
